--- a/artfynd/A 34164-2023 artfynd.xlsx
+++ b/artfynd/A 34164-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 34164-2023 artfynd.xlsx
+++ b/artfynd/A 34164-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>114046486</v>
       </c>
       <c r="B2" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -777,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114046487</v>
+        <v>114046489</v>
       </c>
       <c r="B3" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>785546</v>
+        <v>785561</v>
       </c>
       <c r="R3" t="n">
-        <v>7362561</v>
+        <v>7362651</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,6 +866,103 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>114046487</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Storkroken-Holmsvattensel, Nb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>785546</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7362561</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-10-22</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-10-22</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Frédéric Forsmark</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34164-2023 artfynd.xlsx
+++ b/artfynd/A 34164-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114046486</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114046489</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,8 +978,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114046487</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>